--- a/Solved Questions.xlsx
+++ b/Solved Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mr.chiragbhisikar/Desktop/DSA---365-Day-Of-Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF51D89-66C9-FA4C-8503-F42057896629}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321782A-0703-444A-8C15-26FA53298B26}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{BDF204E7-E28E-4846-A196-A00BA9D827E3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
   <si>
     <t>Topic:</t>
   </si>
@@ -199,6 +199,33 @@
   </si>
   <si>
     <t>Find Missing Number From 1 To N</t>
+  </si>
+  <si>
+    <t>Find The Single Number</t>
+  </si>
+  <si>
+    <t>Longest subarray with given sum K(positives)</t>
+  </si>
+  <si>
+    <t>Longest subarray with sum K (Positives + Negatives)</t>
+  </si>
+  <si>
+    <t>Two Sum</t>
+  </si>
+  <si>
+    <t>Leetcode 1</t>
+  </si>
+  <si>
+    <t>Majority Element</t>
+  </si>
+  <si>
+    <t>Moore's Voting Algorithm</t>
+  </si>
+  <si>
+    <t>Maximum Subarray Sum</t>
+  </si>
+  <si>
+    <t>Kadane's Algorithm</t>
   </si>
 </sst>
 </file>
@@ -253,13 +280,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="1"/>
@@ -296,6 +316,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -324,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -341,15 +369,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -665,13 +699,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C186E7A1-A017-EA41-938C-347AD2E30379}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.1640625" customWidth="1"/>
     <col min="3" max="3" width="88" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26">
@@ -706,7 +741,7 @@
       <c r="C6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -720,7 +755,7 @@
       <c r="C7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -734,7 +769,7 @@
       <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -748,7 +783,7 @@
       <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -762,7 +797,7 @@
       <c r="C10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -776,7 +811,7 @@
       <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -787,10 +822,10 @@
       <c r="B12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -804,7 +839,7 @@
       <c r="C13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -815,10 +850,10 @@
       <c r="B14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -829,10 +864,10 @@
       <c r="B15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -846,7 +881,7 @@
       <c r="C16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -857,10 +892,10 @@
       <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -947,7 +982,7 @@
       <c r="B27" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -1024,7 +1059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="21">
+    <row r="33" spans="1:5" ht="21">
       <c r="A33" s="6" t="s">
         <v>43</v>
       </c>
@@ -1038,7 +1073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="21">
+    <row r="34" spans="1:5" ht="21">
       <c r="A34" s="6" t="s">
         <v>43</v>
       </c>
@@ -1052,7 +1087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="21">
+    <row r="35" spans="1:5" ht="21">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
@@ -1066,7 +1101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="21">
+    <row r="36" spans="1:5" ht="21">
       <c r="A36" s="6" t="s">
         <v>43</v>
       </c>
@@ -1080,159 +1115,229 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="21">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="5"/>
-    </row>
-    <row r="38" spans="1:4" ht="21">
-      <c r="C38" s="8"/>
+    <row r="37" spans="1:5" ht="21">
+      <c r="A37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="22">
+      <c r="A38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="D38" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="21">
+      <c r="A39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="22">
+      <c r="A40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="24">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="24">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="21">
+      <c r="A60" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="8"/>
+      <c r="C60" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="21">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="5" t="s">
+    <row r="61" spans="1:4" ht="21">
+      <c r="A61" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="8"/>
+      <c r="C61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="21">
-      <c r="A40" s="9" t="s">
+    <row r="62" spans="1:4" ht="21">
+      <c r="A62" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="B62" s="8"/>
+      <c r="C62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="21">
-      <c r="A41" s="9" t="s">
+    <row r="63" spans="1:4" ht="21">
+      <c r="A63" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="B63" s="8"/>
+      <c r="C63" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="21">
-      <c r="A42" s="9" t="s">
+    <row r="64" spans="1:4" ht="21">
+      <c r="A64" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="B64" s="8"/>
+      <c r="C64" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="21">
-      <c r="A43" s="9" t="s">
+    <row r="65" spans="1:4" ht="21">
+      <c r="A65" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="B65" s="8"/>
+      <c r="C65" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="21">
-      <c r="A44" s="9" t="s">
+    <row r="66" spans="1:4" ht="21">
+      <c r="A66" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="B66" s="8"/>
+      <c r="C66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="21">
-      <c r="A45" s="9" t="s">
+    <row r="67" spans="1:4" ht="21">
+      <c r="A67" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="B67" s="8"/>
+      <c r="C67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="21">
-      <c r="A46" s="9" t="s">
+    <row r="68" spans="1:4" ht="21">
+      <c r="A68" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="B68" s="8"/>
+      <c r="C68" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="21">
-      <c r="A47" s="9" t="s">
+    <row r="69" spans="1:4" ht="21">
+      <c r="A69" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="5" t="s">
+      <c r="B69" s="8"/>
+      <c r="C69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="21">
-      <c r="A48" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="21">
-      <c r="A49" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C40" r:id="rId1" xr:uid="{4DCCBE38-CD62-8344-90CC-4ED48DA99F80}"/>
-    <hyperlink ref="C41" r:id="rId2" xr:uid="{673C0072-64A9-B744-92DA-1B3C61C254CA}"/>
-    <hyperlink ref="C42" r:id="rId3" xr:uid="{AA3B0F83-53C4-4649-9C91-62990640DEB7}"/>
-    <hyperlink ref="C43" r:id="rId4" xr:uid="{88ADEE89-50D0-D34C-9310-C78CA2E76C25}"/>
-    <hyperlink ref="C44" r:id="rId5" xr:uid="{FD578087-1F6C-F749-941B-970976C0B928}"/>
-    <hyperlink ref="C45" r:id="rId6" xr:uid="{B7D30E2F-0350-5147-BF25-92077D5173FA}"/>
-    <hyperlink ref="C46" r:id="rId7" xr:uid="{2D3B042A-7189-5543-95CA-16F5B708A279}"/>
-    <hyperlink ref="C47" r:id="rId8" xr:uid="{7CF0E18C-E81E-D740-8039-11F147794442}"/>
-    <hyperlink ref="C48" r:id="rId9" xr:uid="{7E9BFB62-8AEF-E84A-A1E1-6BFF03D0403A}"/>
-    <hyperlink ref="C49" r:id="rId10" xr:uid="{6428B547-E964-9346-AF2A-BDA40A3E7622}"/>
+    <hyperlink ref="C60" r:id="rId1" xr:uid="{4DCCBE38-CD62-8344-90CC-4ED48DA99F80}"/>
+    <hyperlink ref="C61" r:id="rId2" xr:uid="{673C0072-64A9-B744-92DA-1B3C61C254CA}"/>
+    <hyperlink ref="C62" r:id="rId3" xr:uid="{AA3B0F83-53C4-4649-9C91-62990640DEB7}"/>
+    <hyperlink ref="C63" r:id="rId4" xr:uid="{88ADEE89-50D0-D34C-9310-C78CA2E76C25}"/>
+    <hyperlink ref="C64" r:id="rId5" xr:uid="{FD578087-1F6C-F749-941B-970976C0B928}"/>
+    <hyperlink ref="C65" r:id="rId6" xr:uid="{B7D30E2F-0350-5147-BF25-92077D5173FA}"/>
+    <hyperlink ref="C66" r:id="rId7" xr:uid="{2D3B042A-7189-5543-95CA-16F5B708A279}"/>
+    <hyperlink ref="C67" r:id="rId8" xr:uid="{7CF0E18C-E81E-D740-8039-11F147794442}"/>
+    <hyperlink ref="C68" r:id="rId9" xr:uid="{7E9BFB62-8AEF-E84A-A1E1-6BFF03D0403A}"/>
+    <hyperlink ref="C69" r:id="rId10" xr:uid="{6428B547-E964-9346-AF2A-BDA40A3E7622}"/>
     <hyperlink ref="C11" r:id="rId11" xr:uid="{EC22FC5A-E7B3-0B4C-B06A-CED083DF65CF}"/>
     <hyperlink ref="C8" r:id="rId12" xr:uid="{1BD6009A-2C24-5745-A2C9-D0FC02E3676E}"/>
     <hyperlink ref="C6" r:id="rId13" xr:uid="{081CE045-F4D0-6D47-B40C-293689BA7DBC}"/>
@@ -1250,6 +1355,9 @@
     <hyperlink ref="C28" r:id="rId25" xr:uid="{5E89A263-0EAD-324B-BB51-A820A635B457}"/>
     <hyperlink ref="C29" r:id="rId26" xr:uid="{4DDF63B1-ED10-5E47-BBEA-63B667532AEC}"/>
     <hyperlink ref="C30" r:id="rId27" xr:uid="{3A4CD5F8-0964-E442-9667-646D21AC5879}"/>
+    <hyperlink ref="C39" r:id="rId28" display="https://takeuforward.org/arrays/longest-subarray-with-sum-k-postives-and-negatives/" xr:uid="{99C6D313-484B-EC4F-952A-24D17A261733}"/>
+    <hyperlink ref="C41" r:id="rId29" xr:uid="{02B1FBD9-9BFC-1443-A941-1D98DEFE136F}"/>
+    <hyperlink ref="C42" r:id="rId30" xr:uid="{6B4F477E-3D5B-954D-92B7-BC37E52DF32A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
